--- a/data/trans_orig/P43C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P43C-Provincia-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>129510</t>
+          <t>129707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162241</t>
+          <t>163697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129510</t>
+          <t>129707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>162241</t>
+          <t>163697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92340</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125071</t>
+          <t>124874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92340</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125071</t>
+          <t>124874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251430</t>
+          <t>247562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293675</t>
+          <t>292688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>251430</t>
+          <t>247562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>293675</t>
+          <t>292688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203539</t>
+          <t>204526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245784</t>
+          <t>249652</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203539</t>
+          <t>204526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>245784</t>
+          <t>249652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170402</t>
+          <t>169567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206027</t>
+          <t>206961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170402</t>
+          <t>169567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206027</t>
+          <t>206961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>125471</t>
+          <t>124537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161096</t>
+          <t>161931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125471</t>
+          <t>124537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161096</t>
+          <t>161931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189573</t>
+          <t>191340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227621</t>
+          <t>230411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189573</t>
+          <t>191340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227621</t>
+          <t>230411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142112</t>
+          <t>139322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180160</t>
+          <t>178393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142112</t>
+          <t>139322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180160</t>
+          <t>178393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>69741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99587</t>
+          <t>98849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>69741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99587</t>
+          <t>98849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103415</t>
+          <t>104153</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132010</t>
+          <t>133261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103415</t>
+          <t>104153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132010</t>
+          <t>133261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111468</t>
+          <t>110363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>144066</t>
+          <t>142798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111468</t>
+          <t>110363</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144066</t>
+          <t>142798</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130737</t>
+          <t>132005</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163335</t>
+          <t>164440</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130737</t>
+          <t>132005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163335</t>
+          <t>164440</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>380242</t>
+          <t>377828</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>430136</t>
+          <t>427678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>380242</t>
+          <t>377828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>430136</t>
+          <t>427678</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205373</t>
+          <t>207831</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>257681</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205373</t>
+          <t>207831</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>255267</t>
+          <t>257681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>331445</t>
+          <t>331796</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>388754</t>
+          <t>386613</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>331445</t>
+          <t>331796</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>388754</t>
+          <t>386613</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>371955</t>
+          <t>374096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>429264</t>
+          <t>428913</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>371955</t>
+          <t>374096</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>429264</t>
+          <t>428913</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1732279</t>
+          <t>1728222</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1846842</t>
+          <t>1846242</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1732279</t>
+          <t>1728222</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1846842</t>
+          <t>1846242</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1480208</t>
+          <t>1480808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1594771</t>
+          <t>1598828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1480208</t>
+          <t>1480808</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1594771</t>
+          <t>1598828</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>183783</t>
+          <t>184720</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>216081</t>
+          <t>215241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183783</t>
+          <t>184720</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216081</t>
+          <t>215241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63734</t>
+          <t>64574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96032</t>
+          <t>95095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63734</t>
+          <t>64574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96032</t>
+          <t>95095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>357380</t>
+          <t>357418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>398978</t>
+          <t>399267</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>357380</t>
+          <t>357418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>398978</t>
+          <t>399267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119637</t>
+          <t>119348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161235</t>
+          <t>161197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119637</t>
+          <t>119348</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161235</t>
+          <t>161197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173489</t>
+          <t>172502</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211570</t>
+          <t>213104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>173489</t>
+          <t>172502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211570</t>
+          <t>213104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>126930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166545</t>
+          <t>167532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>126930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166545</t>
+          <t>167532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239894</t>
+          <t>240460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>279424</t>
+          <t>278072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>239894</t>
+          <t>240460</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>279424</t>
+          <t>278072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108571</t>
+          <t>109923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148101</t>
+          <t>147535</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108571</t>
+          <t>109923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148101</t>
+          <t>147535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>122445</t>
+          <t>122592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150440</t>
+          <t>150573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122445</t>
+          <t>122592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150440</t>
+          <t>150573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66058</t>
+          <t>65925</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94053</t>
+          <t>93906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66058</t>
+          <t>65925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94053</t>
+          <t>93906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>134632</t>
+          <t>136223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169857</t>
+          <t>167646</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>134632</t>
+          <t>136223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169857</t>
+          <t>167646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110174</t>
+          <t>112385</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145399</t>
+          <t>143808</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>110174</t>
+          <t>112385</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>145399</t>
+          <t>143808</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>413906</t>
+          <t>413105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>464898</t>
+          <t>464161</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>413906</t>
+          <t>413105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>464898</t>
+          <t>464161</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>223020</t>
+          <t>223757</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>274012</t>
+          <t>274813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223020</t>
+          <t>223757</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>274012</t>
+          <t>274813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>503596</t>
+          <t>503359</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>559634</t>
+          <t>560821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>503596</t>
+          <t>503359</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>559634</t>
+          <t>560821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>251813</t>
+          <t>250626</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>307851</t>
+          <t>308088</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>251813</t>
+          <t>250626</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>307851</t>
+          <t>308088</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2233561</t>
+          <t>2233642</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2345963</t>
+          <t>2354668</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4929,12 +4929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2233561</t>
+          <t>2233642</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2345963</t>
+          <t>2354668</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1176390</t>
+          <t>1167685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1288792</t>
+          <t>1288711</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1176390</t>
+          <t>1167685</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1288792</t>
+          <t>1288711</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -5307,12 +5307,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>185082</t>
+          <t>186867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>217245</t>
+          <t>217120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>185082</t>
+          <t>186867</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217245</t>
+          <t>217120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,42%</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66870</t>
+          <t>66995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99033</t>
+          <t>97248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66870</t>
+          <t>66995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99033</t>
+          <t>97248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>360140</t>
+          <t>361768</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>403533</t>
+          <t>404177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360140</t>
+          <t>361768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>403533</t>
+          <t>404177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116943</t>
+          <t>116299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160336</t>
+          <t>158708</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116943</t>
+          <t>116299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160336</t>
+          <t>158708</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -5783,12 +5783,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>244374</t>
+          <t>246399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274985</t>
+          <t>275448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5798,12 +5798,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>244374</t>
+          <t>246399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>274985</t>
+          <t>275448</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5861,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56624</t>
+          <t>56161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87235</t>
+          <t>85210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5876,12 +5876,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56624</t>
+          <t>56161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87235</t>
+          <t>85210</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>251993</t>
+          <t>248912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>288918</t>
+          <t>287176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251993</t>
+          <t>248912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>288918</t>
+          <t>287176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,38%</t>
         </is>
       </c>
     </row>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97160</t>
+          <t>98902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134085</t>
+          <t>137166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97160</t>
+          <t>98902</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134085</t>
+          <t>137166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81733</t>
+          <t>80751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109025</t>
+          <t>109449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81733</t>
+          <t>80751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109025</t>
+          <t>109449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106704</t>
+          <t>106280</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>133996</t>
+          <t>134978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6352,12 +6352,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106704</t>
+          <t>106280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133996</t>
+          <t>134978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -6497,12 +6497,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50459</t>
+          <t>49515</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78286</t>
+          <t>76466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50459</t>
+          <t>49515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78286</t>
+          <t>76466</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -6575,12 +6575,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>192191</t>
+          <t>194011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>220018</t>
+          <t>220962</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192191</t>
+          <t>194011</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220018</t>
+          <t>220962</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>393380</t>
+          <t>394157</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>445903</t>
+          <t>445547</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>393380</t>
+          <t>394157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>445903</t>
+          <t>445547</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,7%</t>
         </is>
       </c>
     </row>
@@ -6813,12 +6813,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232300</t>
+          <t>232656</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>284823</t>
+          <t>284046</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232300</t>
+          <t>232656</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284823</t>
+          <t>284046</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,88%</t>
         </is>
       </c>
     </row>
@@ -6973,12 +6973,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>519558</t>
+          <t>518203</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>573858</t>
+          <t>572801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>519558</t>
+          <t>518203</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>573858</t>
+          <t>572801</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>246125</t>
+          <t>247182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>300425</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7086,12 +7086,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>246125</t>
+          <t>247182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>300425</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -7211,12 +7211,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2183875</t>
+          <t>2178249</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2297736</t>
+          <t>2294711</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2183875</t>
+          <t>2178249</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2297736</t>
+          <t>2294711</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1208936</t>
+          <t>1211961</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1328423</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7324,12 +7324,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1208936</t>
+          <t>1211961</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1322797</t>
+          <t>1328423</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -7619,32 +7619,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182455</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>153317</t>
+          <t>171699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176014</t>
+          <t>189880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7654,32 +7654,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>168954</t>
+          <t>182455</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153317</t>
+          <t>171699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176014</t>
+          <t>189880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -7697,32 +7697,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -7775,17 +7775,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7810,17 +7810,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>186213</t>
+          <t>203754</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7857,32 +7857,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>215453</t>
+          <t>223941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251450</t>
+          <t>259836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7892,32 +7892,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>232783</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>215453</t>
+          <t>223941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>251450</t>
+          <t>259836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>61,79%</t>
         </is>
       </c>
     </row>
@@ -7935,32 +7935,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>164518</t>
+          <t>178784</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145851</t>
+          <t>160690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181848</t>
+          <t>196585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7970,32 +7970,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>164518</t>
+          <t>178784</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145851</t>
+          <t>160690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181848</t>
+          <t>196585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -8013,17 +8013,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>397301</t>
+          <t>420526</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>397301</t>
+          <t>420526</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>397301</t>
+          <t>420526</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8048,17 +8048,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>397301</t>
+          <t>420526</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>397301</t>
+          <t>420526</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>397301</t>
+          <t>420526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8095,32 +8095,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>147483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168752</t>
+          <t>174670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8130,32 +8130,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>160528</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>147483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168752</t>
+          <t>174670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -8173,32 +8173,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>93371</t>
+          <t>94482</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80342</t>
+          <t>80340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107717</t>
+          <t>107527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8208,32 +8208,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93371</t>
+          <t>94482</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80342</t>
+          <t>80340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107717</t>
+          <t>107527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -8251,17 +8251,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>249094</t>
+          <t>255010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>249094</t>
+          <t>255010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>249094</t>
+          <t>255010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8286,17 +8286,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>249094</t>
+          <t>255010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>249094</t>
+          <t>255010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>249094</t>
+          <t>255010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8333,32 +8333,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>290086</t>
+          <t>209662</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>253516</t>
+          <t>187978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>332305</t>
+          <t>225514</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>290086</t>
+          <t>209662</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253516</t>
+          <t>187978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>332305</t>
+          <t>225514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -8411,32 +8411,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>92055</t>
+          <t>107645</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>91793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128625</t>
+          <t>129329</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8446,32 +8446,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>92055</t>
+          <t>107645</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>91793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128625</t>
+          <t>129329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>40,76%</t>
         </is>
       </c>
     </row>
@@ -8489,17 +8489,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>382141</t>
+          <t>317307</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>382141</t>
+          <t>317307</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>382141</t>
+          <t>317307</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382141</t>
+          <t>317307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382141</t>
+          <t>317307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382141</t>
+          <t>317307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8571,32 +8571,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>59724</t>
+          <t>64951</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51736</t>
+          <t>57128</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66797</t>
+          <t>74032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8606,32 +8606,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59724</t>
+          <t>64951</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51736</t>
+          <t>57128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66797</t>
+          <t>74032</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -8649,32 +8649,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>90497</t>
+          <t>99626</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83424</t>
+          <t>90545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98485</t>
+          <t>107449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8684,32 +8684,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90497</t>
+          <t>99626</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83424</t>
+          <t>90545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98485</t>
+          <t>107449</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,29%</t>
         </is>
       </c>
     </row>
@@ -8727,17 +8727,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>150221</t>
+          <t>164577</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>150221</t>
+          <t>164577</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150221</t>
+          <t>164577</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8762,17 +8762,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>150221</t>
+          <t>164577</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>150221</t>
+          <t>164577</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150221</t>
+          <t>164577</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8809,32 +8809,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75442</t>
+          <t>77185</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97405</t>
+          <t>99909</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,32 +8844,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>86104</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75442</t>
+          <t>77185</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97405</t>
+          <t>99909</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -8887,32 +8887,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>122973</t>
+          <t>125729</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111672</t>
+          <t>114740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133635</t>
+          <t>137464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8922,32 +8922,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>122973</t>
+          <t>125729</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111672</t>
+          <t>114740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>133635</t>
+          <t>137464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -8965,17 +8965,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>209077</t>
+          <t>214649</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>209077</t>
+          <t>214649</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>209077</t>
+          <t>214649</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>209077</t>
+          <t>214649</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>209077</t>
+          <t>214649</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>209077</t>
+          <t>214649</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9047,32 +9047,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>337046</t>
+          <t>394812</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142939</t>
+          <t>371274</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>496637</t>
+          <t>412274</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9082,32 +9082,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>337046</t>
+          <t>394812</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142939</t>
+          <t>371274</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>496637</t>
+          <t>412274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -9125,32 +9125,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>319909</t>
+          <t>140580</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>160318</t>
+          <t>123118</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>514016</t>
+          <t>164118</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9160,32 +9160,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>319909</t>
+          <t>140580</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>160318</t>
+          <t>123118</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>514016</t>
+          <t>164118</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -9203,17 +9203,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>656955</t>
+          <t>535392</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>656955</t>
+          <t>535392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>656955</t>
+          <t>535392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9238,17 +9238,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>656955</t>
+          <t>535392</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>656955</t>
+          <t>535392</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>656955</t>
+          <t>535392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9285,32 +9285,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>240870</t>
+          <t>267526</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>220180</t>
+          <t>245719</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>260079</t>
+          <t>290264</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9320,32 +9320,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>240870</t>
+          <t>267526</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>220180</t>
+          <t>245719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>260079</t>
+          <t>290264</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -9363,32 +9363,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>335556</t>
+          <t>401141</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>316347</t>
+          <t>378403</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>356246</t>
+          <t>422948</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9398,32 +9398,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>335556</t>
+          <t>401141</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>316347</t>
+          <t>378403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>356246</t>
+          <t>422948</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -9441,17 +9441,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>576426</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>576426</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>576426</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9476,17 +9476,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>576426</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>576426</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>576426</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1180025</t>
+          <t>1564073</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1722853</t>
+          <t>1661715</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1571289</t>
+          <t>1610595</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1180025</t>
+          <t>1564073</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1722853</t>
+          <t>1661715</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1236139</t>
+          <t>1169287</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1084575</t>
+          <t>1118167</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1627403</t>
+          <t>1215809</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1236139</t>
+          <t>1169287</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1084575</t>
+          <t>1118167</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1627403</t>
+          <t>1215809</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -9679,17 +9679,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9714,17 +9714,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2807428</t>
+          <t>2779882</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
